--- a/artfynd/A 20322-2022 artfynd.xlsx
+++ b/artfynd/A 20322-2022 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134016159</v>
+        <v>134016135</v>
       </c>
       <c r="B6" t="n">
-        <v>89340</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grytsjö, Ås lm</t>
+          <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526717</v>
+        <v>526778</v>
       </c>
       <c r="R6" t="n">
-        <v>7209668</v>
+        <v>7209223</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134016135</v>
+        <v>134016159</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>89340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Grytsjön, Ås lm</t>
+          <t>Grytsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526778</v>
+        <v>526717</v>
       </c>
       <c r="R7" t="n">
-        <v>7209223</v>
+        <v>7209668</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134016132</v>
+        <v>134016145</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,39 +1456,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526729</v>
+        <v>526765</v>
       </c>
       <c r="R9" t="n">
-        <v>7209302</v>
+        <v>7209183</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1520,7 +1515,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1525,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134016145</v>
+        <v>134016132</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,34 +1563,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526765</v>
+        <v>526729</v>
       </c>
       <c r="R10" t="n">
-        <v>7209183</v>
+        <v>7209302</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 20322-2022 artfynd.xlsx
+++ b/artfynd/A 20322-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134016157</v>
+        <v>134016154</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -709,7 +713,7 @@
         <v>526736</v>
       </c>
       <c r="R2" t="n">
-        <v>7209664</v>
+        <v>7209667</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134016154</v>
+        <v>134016157</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>91987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,23 +793,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>526736</v>
       </c>
       <c r="R3" t="n">
-        <v>7209667</v>
+        <v>7209664</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1000,7 +1000,7 @@
         <v>134016155</v>
       </c>
       <c r="B5" t="n">
-        <v>92306</v>
+        <v>92313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134016135</v>
+        <v>134016159</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>89347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Grytsjön, Ås lm</t>
+          <t>Grytsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526778</v>
+        <v>526717</v>
       </c>
       <c r="R6" t="n">
-        <v>7209223</v>
+        <v>7209668</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134016159</v>
+        <v>134016135</v>
       </c>
       <c r="B7" t="n">
-        <v>89340</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grytsjö, Ås lm</t>
+          <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526717</v>
+        <v>526778</v>
       </c>
       <c r="R7" t="n">
-        <v>7209668</v>
+        <v>7209223</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134016145</v>
+        <v>134016132</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,34 +1456,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526765</v>
+        <v>526729</v>
       </c>
       <c r="R9" t="n">
-        <v>7209183</v>
+        <v>7209302</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1515,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1525,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134016132</v>
+        <v>134016145</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,39 +1568,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526729</v>
+        <v>526765</v>
       </c>
       <c r="R10" t="n">
-        <v>7209302</v>
+        <v>7209183</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,7 +1667,7 @@
         <v>134016143</v>
       </c>
       <c r="B11" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>134016134</v>
       </c>
       <c r="B12" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>134016161</v>
       </c>
       <c r="B13" t="n">
-        <v>92781</v>
+        <v>92788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 20322-2022 artfynd.xlsx
+++ b/artfynd/A 20322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134016154</v>
+        <v>134016159</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526736</v>
+        <v>526717</v>
       </c>
       <c r="R2" t="n">
-        <v>7209667</v>
+        <v>7209668</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,30 +782,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134016157</v>
+        <v>134016161</v>
       </c>
       <c r="B3" t="n">
-        <v>91987</v>
+        <v>92795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Laurilia sulcata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Burt) Pouzar</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526736</v>
+        <v>526716</v>
       </c>
       <c r="R3" t="n">
-        <v>7209664</v>
+        <v>7209657</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -848,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -858,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134016133</v>
+        <v>134016143</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526761</v>
+        <v>526782</v>
       </c>
       <c r="R4" t="n">
-        <v>7209263</v>
+        <v>7209187</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -960,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,45 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134016155</v>
+        <v>134016134</v>
       </c>
       <c r="B5" t="n">
-        <v>92313</v>
+        <v>83222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grytsjö, Ås lm</t>
+          <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526733</v>
+        <v>526777</v>
       </c>
       <c r="R5" t="n">
-        <v>7209669</v>
+        <v>7209223</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,21 +1087,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1112,39 +1096,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134016159</v>
+        <v>134016155</v>
       </c>
       <c r="B6" t="n">
-        <v>89347</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526717</v>
+        <v>526733</v>
       </c>
       <c r="R6" t="n">
-        <v>7209668</v>
+        <v>7209669</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1189,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,6 +1194,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1229,11 +1228,11 @@
         <v>134016135</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1333,50 +1332,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134016148</v>
+        <v>134016145</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526811</v>
+        <v>526765</v>
       </c>
       <c r="R8" t="n">
-        <v>7209348</v>
+        <v>7209183</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1408,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1418,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,50 +1439,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134016132</v>
+        <v>134016154</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Grytsjön, Ås lm</t>
+          <t>Grytsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526729</v>
+        <v>526736</v>
       </c>
       <c r="R9" t="n">
-        <v>7209302</v>
+        <v>7209667</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1515,22 +1504,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,17 +1539,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134016145</v>
+        <v>134016132</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526765</v>
+        <v>526729</v>
       </c>
       <c r="R10" t="n">
-        <v>7209183</v>
+        <v>7209302</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1627,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134016143</v>
+        <v>134016133</v>
       </c>
       <c r="B11" t="n">
-        <v>91963</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,34 +1669,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526782</v>
+        <v>526761</v>
       </c>
       <c r="R11" t="n">
-        <v>7209187</v>
+        <v>7209263</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1734,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134016134</v>
+        <v>134016148</v>
       </c>
       <c r="B12" t="n">
-        <v>83215</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,34 +1781,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Grytsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526777</v>
+        <v>526811</v>
       </c>
       <c r="R12" t="n">
-        <v>7209223</v>
+        <v>7209348</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1841,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,113 +1879,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>134016161</v>
-      </c>
-      <c r="B13" t="n">
-        <v>92788</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>918</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tajgaskinn</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Laurilia sulcata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Grytsjö, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>526716</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7209657</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Sara Forsström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
